--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI144"/>
+  <dimension ref="A1:BI149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46129.52083333334</v>
+        <v>46129.5</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46129.53125</v>
+        <v>46129.52083333334</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46129.54166666666</v>
+        <v>46129.53125</v>
       </c>
     </row>
     <row r="28">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46129.55555555555</v>
+        <v>46129.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46129.5625</v>
+        <v>46129.55555555555</v>
       </c>
     </row>
     <row r="37">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.5625</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.57291666666</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.57291666666</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.57291666666</v>
       </c>
     </row>
     <row r="44">
@@ -9022,27 +9022,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.57291666666</v>
       </c>
     </row>
     <row r="45">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10007,27 +10007,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="51">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12765,27 +12765,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46129.61458333334</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="66">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="67">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="68">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.61458333334</v>
       </c>
     </row>
     <row r="69">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18281,27 +18281,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46129.63541666666</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46129.63541666666</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="93">
@@ -18675,27 +18675,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="95">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="96">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.63541666666</v>
       </c>
     </row>
     <row r="97">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.63541666666</v>
       </c>
     </row>
     <row r="98">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -20645,27 +20645,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -20842,27 +20842,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="105">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46129.66666666666</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="112">
@@ -22418,27 +22418,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46129.66666666666</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="113">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46129.66666666666</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="114">
@@ -22812,12 +22812,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46129.69791666666</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="115">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46129.70833333334</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="116">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46129.83333333334</v>
+        <v>46129.66666666666</v>
       </c>
     </row>
     <row r="117">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.66666666666</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.66666666666</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.69791666666</v>
       </c>
     </row>
     <row r="120">
@@ -23994,27 +23994,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.70833333334</v>
       </c>
     </row>
     <row r="121">
@@ -24191,27 +24191,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.83333333334</v>
       </c>
     </row>
     <row r="122">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28525,27 +28525,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28713,7 +28713,7 @@
         <v>0</v>
       </c>
       <c r="BI143" s="3" t="n">
-        <v>46129.95833333334</v>
+        <v>46129.875</v>
       </c>
     </row>
     <row r="144">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,141 +28775,1126 @@
         </is>
       </c>
       <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI144" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI145" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Neftchi</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI146" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Rudeš</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Hrvace</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI147" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI148" s="3" t="n">
+        <v>46129.95833333334</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q144" t="n">
+      <c r="Q149" t="n">
         <v>7.39</v>
       </c>
-      <c r="R144" t="n">
+      <c r="R149" t="n">
         <v>10.2</v>
       </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI144" s="3" t="n">
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI149" s="3" t="n">
         <v>46129.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI149"/>
+  <dimension ref="A1:BI159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>2.66</v>
+        <v>2.31</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R98" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.32</v>
+        <v>7.19</v>
       </c>
       <c r="R106" t="n">
-        <v>5.54</v>
+        <v>10.8</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46129.83333333334</v>
+        <v>46129.79166666666</v>
       </c>
     </row>
     <row r="122">
@@ -24388,27 +24388,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.83333333334</v>
       </c>
     </row>
     <row r="123">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29510,27 +29510,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46129.95833333334</v>
+        <v>46129.875</v>
       </c>
     </row>
     <row r="149">
@@ -29707,27 +29707,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,141 +29760,2111 @@
         </is>
       </c>
       <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI149" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Dinamo Jug</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Trajal Krusevac</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI150" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Cibalia</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Karlovac 1919</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI151" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vojvodina</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI152" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>IMT Novi Beograd</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>LFK Mladost Lučani</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI153" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Bijelo Brdo</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Jarun</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI154" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>FAP</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI155" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Orijent 1919</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Opatija</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI156" s="3" t="n">
+        <v>46129.875</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI157" s="3" t="n">
+        <v>46129.89583333334</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI158" s="3" t="n">
+        <v>46129.95833333334</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q149" t="n">
+      <c r="Q159" t="n">
         <v>7.39</v>
       </c>
-      <c r="R149" t="n">
+      <c r="R159" t="n">
         <v>10.2</v>
       </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI149" s="3" t="n">
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI159" s="3" t="n">
         <v>46129.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G156" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G156" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R54" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="R59" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.32</v>
+        <v>7.19</v>
       </c>
       <c r="R107" t="n">
-        <v>5.54</v>
+        <v>10.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G156" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="R54" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>3.22</v>
+        <v>2.66</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="R58" t="n">
-        <v>3.77</v>
+        <v>2.46</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="R60" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.66</v>
+        <v>3.87</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.13</v>
+        <v>3.44</v>
       </c>
       <c r="R61" t="n">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="R63" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R103" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G156" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.18</v>
+        <v>3.12</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>3.22</v>
+        <v>2.31</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="R58" t="n">
-        <v>2.46</v>
+        <v>3.77</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,17 +12617,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="R63" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="R86" t="n">
-        <v>2.79</v>
+        <v>2.44</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R104" t="n">
-        <v>2.33</v>
+        <v>3.23</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G156" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI159"/>
+  <dimension ref="A1:BI155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="R57" t="n">
-        <v>2.31</v>
+        <v>3.77</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.87</v>
+        <v>2.66</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.44</v>
+        <v>3.13</v>
       </c>
       <c r="R61" t="n">
-        <v>1.88</v>
+        <v>2.66</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,17 +12617,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="R63" t="n">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.18</v>
+        <v>2.72</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="R64" t="n">
-        <v>3.22</v>
+        <v>2.46</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R65" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q66" t="n">
         <v>3.05</v>
       </c>
       <c r="R66" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.82</v>
+        <v>3.07</v>
       </c>
       <c r="R81" t="n">
-        <v>4.71</v>
+        <v>2.79</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30495,27 +30495,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.89583333334</v>
       </c>
     </row>
     <row r="154">
@@ -30692,27 +30692,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.95833333334</v>
       </c>
     </row>
     <row r="155">
@@ -30889,27 +30889,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31077,794 +31077,6 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46129.875</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Russia FNL</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Chayka</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Fakel</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N156" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" t="n">
-        <v>0</v>
-      </c>
-      <c r="W156" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI156" s="3" t="n">
-        <v>46129.875</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>CS Emelec</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Guayaquil City FC</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N157" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" t="n">
-        <v>0</v>
-      </c>
-      <c r="W157" t="n">
-        <v>0</v>
-      </c>
-      <c r="X157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI157" s="3" t="n">
-        <v>46129.89583333334</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>St. Louis City II</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N158" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" t="n">
-        <v>0</v>
-      </c>
-      <c r="W158" t="n">
-        <v>0</v>
-      </c>
-      <c r="X158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI158" s="3" t="n">
-        <v>46129.95833333334</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P159" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="R159" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S159" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" t="n">
-        <v>0</v>
-      </c>
-      <c r="W159" t="n">
-        <v>0</v>
-      </c>
-      <c r="X159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI159" s="3" t="n">
         <v>46129.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R57" t="n">
-        <v>3.77</v>
+        <v>2.45</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="R61" t="n">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.93</v>
+        <v>1.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="R62" t="n">
-        <v>2.45</v>
+        <v>3.77</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="R64" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="R65" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R66" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="R81" t="n">
-        <v>2.79</v>
+        <v>2.44</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.44</v>
+        <v>3.09</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R102" t="n">
-        <v>3.23</v>
+        <v>2.37</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.32</v>
+        <v>4.55</v>
       </c>
       <c r="R113" t="n">
-        <v>5.54</v>
+        <v>7.8</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>4.38</v>
+        <v>2.7</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="R57" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.72</v>
+        <v>3.87</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="R58" t="n">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="R61" t="n">
-        <v>3.18</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="R62" t="n">
-        <v>3.77</v>
+        <v>3.18</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="R65" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="R66" t="n">
-        <v>2.31</v>
+        <v>3.77</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.44</v>
+        <v>3.09</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R103" t="n">
-        <v>3.23</v>
+        <v>2.37</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.94</v>
+        <v>3.64</v>
       </c>
       <c r="R105" t="n">
-        <v>2.92</v>
+        <v>3.96</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4.14</v>
+        <v>1.28</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.32</v>
+        <v>7.19</v>
       </c>
       <c r="R108" t="n">
-        <v>1.91</v>
+        <v>10.8</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="R109" t="n">
-        <v>3.57</v>
+        <v>7.8</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q111" t="n">
-        <v>7.19</v>
+        <v>3.32</v>
       </c>
       <c r="R111" t="n">
-        <v>10.8</v>
+        <v>3.57</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.55</v>
+        <v>3.02</v>
       </c>
       <c r="R113" t="n">
-        <v>7.8</v>
+        <v>3.31</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.32</v>
+        <v>2.94</v>
       </c>
       <c r="R114" t="n">
-        <v>5.54</v>
+        <v>2.92</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28771,7 +28771,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>8.5</v>
       </c>
       <c r="R30" t="n">
-        <v>3.21</v>
+        <v>21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R54" t="n">
-        <v>3.22</v>
+        <v>2.66</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.12</v>
+        <v>3.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="R55" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="R61" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="R62" t="n">
-        <v>3.18</v>
+        <v>2.46</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="R65" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R66" t="n">
-        <v>3.77</v>
+        <v>2.45</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R99" t="n">
-        <v>4.96</v>
+        <v>3.23</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.86</v>
+        <v>1.65</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R104" t="n">
-        <v>2.33</v>
+        <v>4.96</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.85</v>
+        <v>4.14</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.64</v>
+        <v>3.32</v>
       </c>
       <c r="R105" t="n">
-        <v>3.96</v>
+        <v>1.91</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.55</v>
+        <v>3.64</v>
       </c>
       <c r="R109" t="n">
-        <v>7.8</v>
+        <v>3.96</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.94</v>
+        <v>4.55</v>
       </c>
       <c r="R114" t="n">
-        <v>2.92</v>
+        <v>7.8</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.28</v>
+        <v>3.56</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="R117" t="n">
-        <v>3.19</v>
+        <v>1.99</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R118" t="n">
-        <v>1.99</v>
+        <v>3.19</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28771,7 +28771,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>3.21</v>
+        <v>4.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="R55" t="n">
-        <v>1.88</v>
+        <v>3.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.18</v>
+        <v>2.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="R56" t="n">
-        <v>3.22</v>
+        <v>2.46</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="R59" t="n">
-        <v>2.31</v>
+        <v>3.77</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R60" t="n">
-        <v>3.77</v>
+        <v>2.45</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="R61" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q66" t="n">
         <v>3.05</v>
       </c>
       <c r="R66" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="R67" t="n">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="R99" t="n">
-        <v>3.23</v>
+        <v>2.33</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.09</v>
+        <v>1.65</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R103" t="n">
-        <v>2.37</v>
+        <v>4.96</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.65</v>
+        <v>3.09</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R104" t="n">
-        <v>4.96</v>
+        <v>2.37</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="R105" t="n">
-        <v>1.91</v>
+        <v>3.31</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.32</v>
+        <v>3.64</v>
       </c>
       <c r="R107" t="n">
-        <v>5.54</v>
+        <v>3.96</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="R113" t="n">
-        <v>3.31</v>
+        <v>3.57</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.55</v>
+        <v>2.94</v>
       </c>
       <c r="R114" t="n">
-        <v>7.8</v>
+        <v>2.92</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>4.38</v>
+        <v>2.7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.07</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>21</v>
+        <v>2.93</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>2.66</v>
+        <v>2.31</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="R55" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R58" t="n">
-        <v>3.22</v>
+        <v>2.66</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="R59" t="n">
-        <v>3.77</v>
+        <v>3.18</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="R60" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="R61" t="n">
-        <v>2.3</v>
+        <v>3.77</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.12</v>
+        <v>3.87</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="R67" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R99" t="n">
-        <v>2.33</v>
+        <v>3.23</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="R101" t="n">
-        <v>3.23</v>
+        <v>2.33</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.3</v>
+        <v>4.14</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="R105" t="n">
-        <v>3.31</v>
+        <v>1.91</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.32</v>
+        <v>3.02</v>
       </c>
       <c r="R106" t="n">
-        <v>5.54</v>
+        <v>3.31</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.64</v>
+        <v>2.94</v>
       </c>
       <c r="R107" t="n">
-        <v>3.96</v>
+        <v>2.92</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="R113" t="n">
-        <v>3.57</v>
+        <v>7.8</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="R114" t="n">
-        <v>2.92</v>
+        <v>5.54</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>4.14</v>
+        <v>1.93</v>
       </c>
       <c r="Q115" t="n">
         <v>3.32</v>
       </c>
       <c r="R115" t="n">
-        <v>1.91</v>
+        <v>3.57</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R117" t="n">
-        <v>1.99</v>
+        <v>3.19</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>4.38</v>
+        <v>2.7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="R54" t="n">
-        <v>2.31</v>
+        <v>3.77</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="Q55" t="n">
         <v>3.05</v>
       </c>
       <c r="R55" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="R59" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R61" t="n">
-        <v>3.77</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.87</v>
+        <v>2.72</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="R67" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>1.77</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R74" t="n">
-        <v>2.36</v>
+        <v>4.38</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="R76" t="n">
-        <v>3.08</v>
+        <v>6.51</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="R79" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.81</v>
+        <v>2.65</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R81" t="n">
-        <v>3.95</v>
+        <v>2.36</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R99" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R102" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4.14</v>
+        <v>1.33</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="R105" t="n">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.55</v>
+        <v>2.94</v>
       </c>
       <c r="R113" t="n">
-        <v>7.8</v>
+        <v>2.92</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.93</v>
+        <v>4.14</v>
       </c>
       <c r="Q115" t="n">
         <v>3.32</v>
       </c>
       <c r="R115" t="n">
-        <v>3.57</v>
+        <v>1.91</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>3.21</v>
+        <v>4.38</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R34" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>3.77</v>
+        <v>3.22</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q55" t="n">
         <v>3.05</v>
       </c>
       <c r="R55" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.37</v>
+        <v>3.13</v>
       </c>
       <c r="R57" t="n">
-        <v>3.18</v>
+        <v>2.66</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="R58" t="n">
-        <v>2.66</v>
+        <v>2.31</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="Q59" t="n">
         <v>3.05</v>
       </c>
       <c r="R59" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="R62" t="n">
-        <v>1.88</v>
+        <v>3.18</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="R64" t="n">
-        <v>3.22</v>
+        <v>3.77</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="R70" t="n">
-        <v>3.63</v>
+        <v>2.79</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
       <c r="R72" t="n">
-        <v>2.93</v>
+        <v>4.71</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>4.38</v>
+        <v>3.08</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R78" t="n">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="R81" t="n">
-        <v>2.36</v>
+        <v>6.51</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R82" t="n">
-        <v>3.95</v>
+        <v>3.02</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R99" t="n">
-        <v>3.12</v>
+        <v>2.33</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.65</v>
+        <v>3.09</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R100" t="n">
-        <v>4.96</v>
+        <v>2.37</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R101" t="n">
-        <v>2.33</v>
+        <v>3.23</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="R110" t="n">
-        <v>3.57</v>
+        <v>3.96</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.64</v>
+        <v>7.19</v>
       </c>
       <c r="R111" t="n">
-        <v>3.96</v>
+        <v>10.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="R113" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.45</v>
+        <v>3.99</v>
       </c>
       <c r="R116" t="n">
-        <v>1.99</v>
+        <v>5.29</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>4.38</v>
+        <v>3.21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="R54" t="n">
-        <v>3.22</v>
+        <v>3.77</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.87</v>
+        <v>2.18</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>1.88</v>
+        <v>3.22</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="R58" t="n">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="R61" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R64" t="n">
-        <v>3.77</v>
+        <v>2.3</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="R70" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="R71" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="R72" t="n">
-        <v>4.71</v>
+        <v>3.08</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>2.34</v>
+        <v>3.63</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="R81" t="n">
-        <v>6.51</v>
+        <v>2.93</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="R82" t="n">
-        <v>3.02</v>
+        <v>4.71</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>3.63</v>
+        <v>2.34</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="R101" t="n">
-        <v>3.23</v>
+        <v>4.96</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R104" t="n">
-        <v>4.96</v>
+        <v>3.12</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.32</v>
+        <v>7.19</v>
       </c>
       <c r="R106" t="n">
-        <v>3.57</v>
+        <v>10.8</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.94</v>
+        <v>3.64</v>
       </c>
       <c r="R107" t="n">
-        <v>2.92</v>
+        <v>3.96</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.55</v>
+        <v>2.94</v>
       </c>
       <c r="R109" t="n">
-        <v>7.8</v>
+        <v>2.92</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Q111" t="n">
-        <v>7.19</v>
+        <v>4.55</v>
       </c>
       <c r="R111" t="n">
-        <v>10.8</v>
+        <v>7.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.32</v>
+        <v>3.02</v>
       </c>
       <c r="R114" t="n">
-        <v>5.54</v>
+        <v>3.31</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.66</v>
+        <v>3.56</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="R116" t="n">
-        <v>5.29</v>
+        <v>1.99</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.18</v>
+        <v>3.99</v>
       </c>
       <c r="R117" t="n">
-        <v>3.19</v>
+        <v>5.29</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,7 +23501,7 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AF117" t="n">
         <v>1.78</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R118" t="n">
-        <v>1.99</v>
+        <v>3.19</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G152" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI155"/>
+  <dimension ref="A1:BI153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>4.38</v>
+        <v>2.93</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>3.21</v>
+        <v>4.38</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="R55" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R56" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="R57" t="n">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="R58" t="n">
-        <v>3.18</v>
+        <v>3.77</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>2.3</v>
+        <v>3.22</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.72</v>
+        <v>3.87</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="R65" t="n">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R66" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="R67" t="n">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="Q70" t="n">
         <v>3.45</v>
       </c>
       <c r="R70" t="n">
-        <v>2.36</v>
+        <v>3.08</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="Q72" t="n">
         <v>3.45</v>
       </c>
       <c r="R72" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R77" t="n">
-        <v>4.38</v>
+        <v>3.95</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="R78" t="n">
-        <v>3.63</v>
+        <v>2.79</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R79" t="n">
-        <v>3.02</v>
+        <v>6.51</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="R81" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="R82" t="n">
-        <v>4.71</v>
+        <v>2.93</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.86</v>
+        <v>3.09</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R98" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.09</v>
+        <v>2.86</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R100" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.32</v>
+        <v>3.02</v>
       </c>
       <c r="R105" t="n">
-        <v>5.54</v>
+        <v>3.31</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.64</v>
+        <v>4.55</v>
       </c>
       <c r="R107" t="n">
-        <v>3.96</v>
+        <v>7.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.94</v>
+        <v>3.64</v>
       </c>
       <c r="R109" t="n">
-        <v>2.92</v>
+        <v>3.96</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.33</v>
+        <v>4.14</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.55</v>
+        <v>3.32</v>
       </c>
       <c r="R111" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="R114" t="n">
-        <v>3.31</v>
+        <v>2.92</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>4.14</v>
+        <v>1.66</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.32</v>
+        <v>4.32</v>
       </c>
       <c r="R115" t="n">
-        <v>1.91</v>
+        <v>5.54</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.45</v>
+        <v>3.99</v>
       </c>
       <c r="R116" t="n">
-        <v>1.99</v>
+        <v>5.29</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.66</v>
+        <v>3.56</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="R117" t="n">
-        <v>5.29</v>
+        <v>1.99</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -30101,12 +30101,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30289,7 +30289,7 @@
         <v>0</v>
       </c>
       <c r="BI151" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.89583333334</v>
       </c>
     </row>
     <row r="152">
@@ -30298,12 +30298,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.95833333334</v>
       </c>
     </row>
     <row r="153">
@@ -30495,12 +30495,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30683,400 +30683,6 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46129.89583333334</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>St. Louis City II</t>
-        </is>
-      </c>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N154" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" t="n">
-        <v>0</v>
-      </c>
-      <c r="T154" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" t="n">
-        <v>0</v>
-      </c>
-      <c r="W154" t="n">
-        <v>0</v>
-      </c>
-      <c r="X154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI154" s="3" t="n">
-        <v>46129.95833333334</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N155" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P155" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="R155" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" t="n">
-        <v>0</v>
-      </c>
-      <c r="W155" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI155" s="3" t="n">
         <v>46129.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.93</v>
+        <v>4.38</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>4.38</v>
+        <v>2.93</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="R55" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="R56" t="n">
-        <v>2.3</v>
+        <v>3.18</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.15</v>
+        <v>3.87</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="R57" t="n">
-        <v>3.18</v>
+        <v>1.88</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.72</v>
+        <v>2.37</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.32</v>
+        <v>2.64</v>
       </c>
       <c r="R62" t="n">
-        <v>2.46</v>
+        <v>3.34</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R64" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.87</v>
+        <v>2.72</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="R65" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="R66" t="n">
-        <v>2.31</v>
+        <v>3.77</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R69" t="n">
-        <v>3.63</v>
+        <v>3.08</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="Q70" t="n">
         <v>3.45</v>
       </c>
       <c r="R70" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>2.36</v>
+        <v>3.63</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="R81" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R82" t="n">
-        <v>2.93</v>
+        <v>4.38</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="R99" t="n">
-        <v>3.23</v>
+        <v>2.33</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R101" t="n">
-        <v>4.96</v>
+        <v>3.23</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.02</v>
+        <v>7.19</v>
       </c>
       <c r="R105" t="n">
-        <v>3.31</v>
+        <v>10.8</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.55</v>
+        <v>3.02</v>
       </c>
       <c r="R107" t="n">
-        <v>7.8</v>
+        <v>3.31</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.85</v>
+        <v>4.14</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.64</v>
+        <v>3.32</v>
       </c>
       <c r="R109" t="n">
-        <v>3.96</v>
+        <v>1.91</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>4.14</v>
+        <v>1.66</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>4.32</v>
       </c>
       <c r="R111" t="n">
-        <v>1.91</v>
+        <v>5.54</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q112" t="n">
-        <v>7.19</v>
+        <v>3.32</v>
       </c>
       <c r="R112" t="n">
-        <v>10.8</v>
+        <v>3.57</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="R113" t="n">
-        <v>3.57</v>
+        <v>3.96</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.94</v>
+        <v>3.52</v>
       </c>
       <c r="R114" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.32</v>
+        <v>2.94</v>
       </c>
       <c r="R115" t="n">
-        <v>5.54</v>
+        <v>2.92</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.66</v>
+        <v>3.56</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="R116" t="n">
-        <v>5.29</v>
+        <v>1.99</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R117" t="n">
-        <v>1.99</v>
+        <v>3.19</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.18</v>
+        <v>3.99</v>
       </c>
       <c r="R118" t="n">
-        <v>3.19</v>
+        <v>5.29</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,7 +23698,7 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AF118" t="n">
         <v>1.78</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G150" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI153"/>
+  <dimension ref="A1:BI147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46129.45138888889</v>
+        <v>46129.4375</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46129.45833333334</v>
+        <v>46129.4375</v>
       </c>
     </row>
     <row r="19">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46129.47916666666</v>
+        <v>46129.45138888889</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46129.47916666666</v>
+        <v>46129.45833333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46129.5</v>
+        <v>46129.47916666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46129.5</v>
+        <v>46129.47916666666</v>
       </c>
     </row>
     <row r="23">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46129.52083333334</v>
+        <v>46129.5</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46129.53125</v>
+        <v>46129.5</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46129.54166666666</v>
+        <v>46129.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46129.54166666666</v>
+        <v>46129.53125</v>
       </c>
     </row>
     <row r="30">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.93</v>
+        <v>4.38</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46129.55555555555</v>
+        <v>46129.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46129.5625</v>
+        <v>46129.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46129.5625</v>
+        <v>46129.55555555555</v>
       </c>
     </row>
     <row r="39">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46129.57291666666</v>
+        <v>46129.5625</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46129.57291666666</v>
+        <v>46129.5625</v>
       </c>
     </row>
     <row r="43">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9219,27 +9219,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.57291666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,27 +9416,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46129.58333333334</v>
+        <v>46129.57291666666</v>
       </c>
     </row>
     <row r="47">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46129.60416666666</v>
+        <v>46129.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="R60" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.18</v>
+        <v>3.12</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R61" t="n">
-        <v>3.22</v>
+        <v>2.31</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="R62" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="R64" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="R65" t="n">
-        <v>2.46</v>
+        <v>3.77</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46129.61458333334</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="69">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.13</v>
+        <v>2.66</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="R69" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.60416666666</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46129.625</v>
+        <v>46129.61458333334</v>
       </c>
     </row>
     <row r="71">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="R71" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R72" t="n">
-        <v>3.63</v>
+        <v>6.51</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R74" t="n">
-        <v>2.44</v>
+        <v>3.63</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="Q75" t="n">
         <v>3.7</v>
       </c>
       <c r="R75" t="n">
-        <v>3.95</v>
+        <v>2.34</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="R80" t="n">
-        <v>6.51</v>
+        <v>4.71</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R81" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R82" t="n">
-        <v>4.38</v>
+        <v>2.93</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46129.63541666666</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="97">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46129.63541666666</v>
+        <v>46129.625</v>
       </c>
     </row>
     <row r="98">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.63541666666</v>
       </c>
     </row>
     <row r="99">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.86</v>
+        <v>2.22</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R99" t="n">
-        <v>2.33</v>
+        <v>3.12</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46129.64583333334</v>
+        <v>46129.63541666666</v>
       </c>
     </row>
     <row r="100">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R103" t="n">
-        <v>3.12</v>
+        <v>2.33</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q105" t="n">
-        <v>7.19</v>
+        <v>3.38</v>
       </c>
       <c r="R105" t="n">
-        <v>10.8</v>
+        <v>3.23</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="106">
@@ -21236,27 +21236,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="R106" t="n">
-        <v>7.8</v>
+        <v>4.96</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46129.65625</v>
+        <v>46129.64583333334</v>
       </c>
     </row>
     <row r="107">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="R107" t="n">
-        <v>3.31</v>
+        <v>2.21</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="R108" t="n">
-        <v>2.21</v>
+        <v>3.96</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>4.14</v>
+        <v>1.66</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.32</v>
+        <v>4.32</v>
       </c>
       <c r="R109" t="n">
-        <v>1.91</v>
+        <v>5.54</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="R110" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.66</v>
+        <v>4.14</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.32</v>
+        <v>3.32</v>
       </c>
       <c r="R111" t="n">
-        <v>5.54</v>
+        <v>1.91</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="R112" t="n">
-        <v>3.57</v>
+        <v>3.31</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.64</v>
+        <v>2.94</v>
       </c>
       <c r="R113" t="n">
-        <v>3.96</v>
+        <v>2.92</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="R114" t="n">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22913,7 +22913,7 @@
         <v>1.79</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.94</v>
+        <v>4.55</v>
       </c>
       <c r="R115" t="n">
-        <v>2.92</v>
+        <v>7.8</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.56</v>
+        <v>1.28</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.45</v>
+        <v>7.19</v>
       </c>
       <c r="R116" t="n">
-        <v>1.99</v>
+        <v>10.8</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46129.66666666666</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="117">
@@ -23403,27 +23403,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46129.66666666666</v>
+        <v>46129.65625</v>
       </c>
     </row>
     <row r="118">
@@ -23797,27 +23797,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.67</v>
+        <v>3.18</v>
       </c>
       <c r="R119" t="n">
-        <v>3.98</v>
+        <v>3.19</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46129.69791666666</v>
+        <v>46129.66666666666</v>
       </c>
     </row>
     <row r="120">
@@ -23994,27 +23994,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46129.70833333334</v>
+        <v>46129.66666666666</v>
       </c>
     </row>
     <row r="121">
@@ -24191,27 +24191,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46129.79166666666</v>
+        <v>46129.69791666666</v>
       </c>
     </row>
     <row r="122">
@@ -24388,12 +24388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46129.83333333334</v>
+        <v>46129.70833333334</v>
       </c>
     </row>
     <row r="123">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.79166666666</v>
       </c>
     </row>
     <row r="124">
@@ -24782,27 +24782,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.83333333334</v>
       </c>
     </row>
     <row r="125">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26013,7 +26013,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28919,27 +28919,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29107,7 +29107,7 @@
         <v>0</v>
       </c>
       <c r="BI145" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.89583333334</v>
       </c>
     </row>
     <row r="146">
@@ -29116,27 +29116,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29304,7 +29304,7 @@
         <v>0</v>
       </c>
       <c r="BI146" s="3" t="n">
-        <v>46129.875</v>
+        <v>46129.95833333334</v>
       </c>
     </row>
     <row r="147">
@@ -29313,27 +29313,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29501,1188 +29501,6 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46129.875</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Mačva Šabac</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N148" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI148" s="3" t="n">
-        <v>46129.875</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Stepojevac Vaga</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI149" s="3" t="n">
-        <v>46129.875</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>FAP</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI150" s="3" t="n">
-        <v>46129.875</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>CS Emelec</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Guayaquil City FC</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" t="n">
-        <v>0</v>
-      </c>
-      <c r="V151" t="n">
-        <v>0</v>
-      </c>
-      <c r="W151" t="n">
-        <v>0</v>
-      </c>
-      <c r="X151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI151" s="3" t="n">
-        <v>46129.89583333334</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>St. Louis City II</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N152" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" t="n">
-        <v>0</v>
-      </c>
-      <c r="V152" t="n">
-        <v>0</v>
-      </c>
-      <c r="W152" t="n">
-        <v>0</v>
-      </c>
-      <c r="X152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI152" s="3" t="n">
-        <v>46129.95833333334</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P153" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="R153" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S153" t="n">
-        <v>0</v>
-      </c>
-      <c r="T153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="n">
-        <v>0</v>
-      </c>
-      <c r="V153" t="n">
-        <v>0</v>
-      </c>
-      <c r="W153" t="n">
-        <v>0</v>
-      </c>
-      <c r="X153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH153" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI153" s="3" t="n">
         <v>46129.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>4.38</v>
+        <v>2.93</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.36</v>
+        <v>1.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.93</v>
+        <v>21</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="R58" t="n">
-        <v>3.22</v>
+        <v>3.77</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.93</v>
+        <v>2.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="R59" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R61" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.37</v>
+        <v>3.87</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.64</v>
+        <v>3.44</v>
       </c>
       <c r="R64" t="n">
-        <v>3.34</v>
+        <v>1.88</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="R65" t="n">
-        <v>3.77</v>
+        <v>2.66</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="R68" t="n">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="R69" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="R72" t="n">
-        <v>6.51</v>
+        <v>3.08</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>3.63</v>
+        <v>2.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="R78" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="R79" t="n">
-        <v>4.38</v>
+        <v>4.71</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="R81" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.86</v>
+        <v>3.09</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R103" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R104" t="n">
-        <v>3.12</v>
+        <v>2.33</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="R107" t="n">
-        <v>2.21</v>
+        <v>3.96</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="R108" t="n">
-        <v>3.96</v>
+        <v>2.21</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.32</v>
+        <v>3.2</v>
       </c>
       <c r="R109" t="n">
-        <v>5.54</v>
+        <v>3.42</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.52</v>
+        <v>7.19</v>
       </c>
       <c r="R110" t="n">
-        <v>3.85</v>
+        <v>10.8</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>4.14</v>
+        <v>1.33</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="R111" t="n">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.02</v>
+        <v>4.32</v>
       </c>
       <c r="R112" t="n">
-        <v>3.31</v>
+        <v>5.54</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.4</v>
+        <v>4.14</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="R113" t="n">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.55</v>
+        <v>3.52</v>
       </c>
       <c r="R115" t="n">
-        <v>7.8</v>
+        <v>3.85</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q116" t="n">
-        <v>7.19</v>
+        <v>3.02</v>
       </c>
       <c r="R116" t="n">
-        <v>10.8</v>
+        <v>3.31</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="R117" t="n">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.66</v>
+        <v>3.56</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="R118" t="n">
-        <v>5.29</v>
+        <v>1.99</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.45</v>
+        <v>3.99</v>
       </c>
       <c r="R120" t="n">
-        <v>1.99</v>
+        <v>5.29</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26013,7 +26013,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G144" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.07</v>
+        <v>2.36</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>21</v>
+        <v>2.93</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>2.7</v>
+        <v>4.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>2.3</v>
+        <v>3.22</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R58" t="n">
-        <v>3.77</v>
+        <v>2.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R60" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,55 +13015,55 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.87</v>
+        <v>1.93</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="R64" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
         <v>1.88</v>
       </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.13</v>
+        <v>2.64</v>
       </c>
       <c r="R65" t="n">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.37</v>
+        <v>3.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="R66" t="n">
-        <v>3.34</v>
+        <v>2.31</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="R67" t="n">
-        <v>3.18</v>
+        <v>2.3</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="R68" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="R79" t="n">
-        <v>4.71</v>
+        <v>3.08</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="R81" t="n">
-        <v>2.44</v>
+        <v>4.38</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R83" t="n">
-        <v>3.02</v>
+        <v>2.93</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R84" t="n">
-        <v>2.93</v>
+        <v>3.63</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R86" t="n">
-        <v>4.38</v>
+        <v>6.51</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R87" t="n">
-        <v>3.63</v>
+        <v>2.44</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.22</v>
+        <v>3.09</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R102" t="n">
-        <v>3.12</v>
+        <v>2.37</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="R104" t="n">
-        <v>2.33</v>
+        <v>3.23</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R105" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.64</v>
+        <v>4.55</v>
       </c>
       <c r="R107" t="n">
-        <v>3.96</v>
+        <v>7.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="R108" t="n">
-        <v>2.21</v>
+        <v>3.85</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="R109" t="n">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q110" t="n">
-        <v>7.19</v>
+        <v>3.32</v>
       </c>
       <c r="R110" t="n">
-        <v>10.8</v>
+        <v>3.57</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.55</v>
+        <v>7.19</v>
       </c>
       <c r="R111" t="n">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.66</v>
+        <v>2.85</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.32</v>
+        <v>3.38</v>
       </c>
       <c r="R112" t="n">
-        <v>5.54</v>
+        <v>2.21</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>4.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>1.91</v>
+        <v>3.42</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="R114" t="n">
-        <v>3.57</v>
+        <v>3.31</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.8</v>
+        <v>4.14</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="R115" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.02</v>
+        <v>3.64</v>
       </c>
       <c r="R116" t="n">
-        <v>3.31</v>
+        <v>3.96</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="R117" t="n">
-        <v>2.92</v>
+        <v>5.54</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R118" t="n">
-        <v>1.99</v>
+        <v>3.19</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.18</v>
+        <v>3.99</v>
       </c>
       <c r="R119" t="n">
-        <v>3.19</v>
+        <v>5.29</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,7 +23895,7 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AF119" t="n">
         <v>1.78</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.66</v>
+        <v>3.56</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="R120" t="n">
-        <v>5.29</v>
+        <v>1.99</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G144" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.5</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>21</v>
+        <v>3.21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="R36" t="n">
-        <v>3.21</v>
+        <v>2.67</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>2.91</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="R55" t="n">
-        <v>3.46</v>
+        <v>2.36</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.87</v>
+        <v>2.37</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.44</v>
+        <v>2.64</v>
       </c>
       <c r="R56" t="n">
-        <v>1.88</v>
+        <v>3.34</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="R58" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="R60" t="n">
-        <v>2.95</v>
+        <v>3.77</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="R63" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="R65" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="R66" t="n">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>2.66</v>
+        <v>3.22</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="R78" t="n">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="R80" t="n">
-        <v>4.71</v>
+        <v>2.93</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="R100" t="n">
-        <v>2.33</v>
+        <v>4.39</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.65</v>
+        <v>2.86</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R101" t="n">
-        <v>4.96</v>
+        <v>2.33</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.09</v>
+        <v>2.22</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R102" t="n">
-        <v>2.37</v>
+        <v>3.12</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.44</v>
+        <v>3.09</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R104" t="n">
-        <v>3.23</v>
+        <v>2.37</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R105" t="n">
-        <v>3.12</v>
+        <v>2.21</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.55</v>
+        <v>7.19</v>
       </c>
       <c r="R107" t="n">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="R108" t="n">
-        <v>3.85</v>
+        <v>3.31</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.4</v>
+        <v>4.14</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="R109" t="n">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="R110" t="n">
-        <v>3.57</v>
+        <v>3.96</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q111" t="n">
-        <v>7.19</v>
+        <v>2.94</v>
       </c>
       <c r="R111" t="n">
-        <v>10.8</v>
+        <v>2.92</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="R112" t="n">
-        <v>2.21</v>
+        <v>3.57</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>4.32</v>
       </c>
       <c r="R113" t="n">
-        <v>3.42</v>
+        <v>5.54</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="R114" t="n">
-        <v>3.31</v>
+        <v>2.21</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>4.14</v>
+        <v>1.33</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="R115" t="n">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>3.96</v>
+        <v>3.42</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="Q117" t="n">
-        <v>4.32</v>
+        <v>3.52</v>
       </c>
       <c r="R117" t="n">
-        <v>5.54</v>
+        <v>3.85</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.66</v>
+        <v>3.56</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="R119" t="n">
-        <v>5.29</v>
+        <v>1.99</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.45</v>
+        <v>3.99</v>
       </c>
       <c r="R120" t="n">
-        <v>1.99</v>
+        <v>5.29</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G144" t="n">

--- a/jogos_2026-04-17.xlsx
+++ b/jogos_2026-04-17.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>8.5</v>
       </c>
       <c r="R35" t="n">
-        <v>3.21</v>
+        <v>21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.32</v>
+        <v>5.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="R36" t="n">
-        <v>2.67</v>
+        <v>1.56</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.5</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>21</v>
+        <v>3.21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.12</v>
+        <v>3.87</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="R59" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="R60" t="n">
-        <v>3.77</v>
+        <v>3.18</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="R61" t="n">
-        <v>2.66</v>
+        <v>3.77</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="R62" t="n">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="R63" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="R65" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="R66" t="n">
-        <v>3.18</v>
+        <v>2.46</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="R69" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R75" t="n">
-        <v>3.63</v>
+        <v>2.93</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="R76" t="n">
-        <v>3.95</v>
+        <v>6.51</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.41</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R77" t="n">
-        <v>6.51</v>
+        <v>3.02</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
       <c r="R79" t="n">
-        <v>3.08</v>
+        <v>4.71</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="R92" t="n">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="R94" t="n">
-        <v>4.71</v>
+        <v>2.85</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R97" t="n">
-        <v>4.38</v>
+        <v>3.95</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="R100" t="n">
-        <v>4.39</v>
+        <v>2.21</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.86</v>
+        <v>1.65</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R101" t="n">
-        <v>2.33</v>
+        <v>4.96</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.22</v>
+        <v>3.09</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R102" t="n">
-        <v>3.12</v>
+        <v>2.37</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.65</v>
+        <v>2.86</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R103" t="n">
-        <v>4.96</v>
+        <v>2.33</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.09</v>
+        <v>2.44</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R104" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R105" t="n">
-        <v>2.21</v>
+        <v>3.12</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.44</v>
+        <v>1.79</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R106" t="n">
-        <v>3.23</v>
+        <v>4.39</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q107" t="n">
-        <v>7.19</v>
+        <v>3.02</v>
       </c>
       <c r="R107" t="n">
-        <v>10.8</v>
+        <v>3.31</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.02</v>
+        <v>4.32</v>
       </c>
       <c r="R108" t="n">
-        <v>3.31</v>
+        <v>5.54</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r=